--- a/safety_inspection_forms/015_inflatable_safety_inspection_checklist--safety_inspection_forms.xlsx
+++ b/safety_inspection_forms/015_inflatable_safety_inspection_checklist--safety_inspection_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1125,8 +1125,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="48" customWidth="1" min="2" max="2"/>
-    <col width="48" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'value':_'excellent'}</t>
+          <t>excellent</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'value': 'Excellent'}</t>
+          <t>Excellent</t>
         </is>
       </c>
     </row>
@@ -1171,12 +1171,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'value':_'fair'}</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'value': 'Fair'}</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'value':_'poor'}</t>
+          <t>poor</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'value': 'Poor'}</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
@@ -1205,12 +1205,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_4,_'value':_'n/a'}</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 4, 'value': 'N/A'}</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -1222,12 +1222,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_1,_'value':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 1, 'value': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1239,12 +1239,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_2,_'value':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 2, 'value': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1256,12 +1256,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_3,_'value':_'not_applicable'}</t>
+          <t>not_applicable</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 3, 'value': 'Not Applicable'}</t>
+          <t>Not Applicable</t>
         </is>
       </c>
     </row>
@@ -1273,12 +1273,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_1,_'value':_'certified'}</t>
+          <t>certified</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 1, 'value': 'Certified'}</t>
+          <t>Certified</t>
         </is>
       </c>
     </row>
@@ -1290,12 +1290,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_2,_'value':_'non-certified'}</t>
+          <t>non-certified</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 2, 'value': 'Non-Certified'}</t>
+          <t>Non-Certified</t>
         </is>
       </c>
     </row>
@@ -1307,12 +1307,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_3,_'value':_'unknown'}</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 3, 'value': 'Unknown'}</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
@@ -1324,12 +1324,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_4,_'value':_'n/a'}</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 4, 'value': 'N/A'}</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -1341,12 +1341,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_1,_'value':_'completed'}</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 1, 'value': 'Completed'}</t>
+          <t>Completed</t>
         </is>
       </c>
     </row>
@@ -1358,12 +1358,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_2,_'value':_'not_completed'}</t>
+          <t>not_completed</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 2, 'value': 'Not Completed'}</t>
+          <t>Not Completed</t>
         </is>
       </c>
     </row>
@@ -1375,12 +1375,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_3,_'value':_'not_required'}</t>
+          <t>not_required</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 3, 'value': 'Not Required'}</t>
+          <t>Not Required</t>
         </is>
       </c>
     </row>
@@ -1392,12 +1392,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_4,_'value':_'n/a'}</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 4, 'value': 'N/A'}</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -1409,12 +1409,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_1,_'value':_'available'}</t>
+          <t>available</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 1, 'value': 'Available'}</t>
+          <t>Available</t>
         </is>
       </c>
     </row>
@@ -1426,12 +1426,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_2,_'value':_'not_available'}</t>
+          <t>not_available</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 2, 'value': 'Not Available'}</t>
+          <t>Not Available</t>
         </is>
       </c>
     </row>
@@ -1443,12 +1443,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_3,_'value':_'partially_available'}</t>
+          <t>partially_available</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 3, 'value': 'Partially Available'}</t>
+          <t>Partially Available</t>
         </is>
       </c>
     </row>
@@ -1460,12 +1460,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'id':_4,_'value':_'n/a'}</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'id': 4, 'value': 'N/A'}</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -1477,12 +1477,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'id':_1,_'value':_'available'}</t>
+          <t>available</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'id': 1, 'value': 'Available'}</t>
+          <t>Available</t>
         </is>
       </c>
     </row>
@@ -1494,12 +1494,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'id':_2,_'value':_'not_available'}</t>
+          <t>not_available</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'id': 2, 'value': 'Not Available'}</t>
+          <t>Not Available</t>
         </is>
       </c>
     </row>
@@ -1511,12 +1511,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'id':_3,_'value':_'partially_available'}</t>
+          <t>partially_available</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'id': 3, 'value': 'Partially Available'}</t>
+          <t>Partially Available</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'id':_4,_'value':_'n/a'}</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'id': 4, 'value': 'N/A'}</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -1545,12 +1545,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'id':_1,_'value':_'clearly_marked'}</t>
+          <t>clearly_marked</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'id': 1, 'value': 'Clearly Marked'}</t>
+          <t>Clearly Marked</t>
         </is>
       </c>
     </row>
@@ -1562,12 +1562,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'id':_2,_'value':_'not_clearly_marked'}</t>
+          <t>not_clearly_marked</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'id': 2, 'value': 'Not Clearly Marked'}</t>
+          <t>Not Clearly Marked</t>
         </is>
       </c>
     </row>
@@ -1579,12 +1579,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'id':_3,_'value':_'partially_clearly_marked'}</t>
+          <t>partially_clearly_marked</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'id': 3, 'value': 'Partially Clearly Marked'}</t>
+          <t>Partially Clearly Marked</t>
         </is>
       </c>
     </row>
@@ -1596,12 +1596,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'id':_4,_'value':_'n/a'}</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'id': 4, 'value': 'N/A'}</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
